--- a/Lama_Israeli_Cyber_Deal_Database_v8.xlsx
+++ b/Lama_Israeli_Cyber_Deal_Database_v8.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deals" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Taxonomy" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Deals" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Taxonomy" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deals'!$A$3:$AB$3</definedName>
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB488"/>
+  <dimension ref="A1:AB489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -49972,6 +49972,108 @@
         </is>
       </c>
     </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Dream Security</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>dream.security</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>https://my.pitchbook.com/profile/510561-82/company/profile</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>AI-powered cyber defense — autonomous threat detection at national and enterprise scale</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>Tel Aviv</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>Security Operations</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>Shalev Hulio</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>8200</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>NSO Group (co-founder)</t>
+        </is>
+      </c>
+      <c r="O489" t="inlineStr">
+        <is>
+          <t>Government, critical infrastructure</t>
+        </is>
+      </c>
+      <c r="P489" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="Q489" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="R489" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U489" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="V489" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="W489" t="inlineStr">
+        <is>
+          <t>260.0</t>
+        </is>
+      </c>
+      <c r="AA489" t="inlineStr">
+        <is>
+          <t>https://en.globes.co.il/test</t>
+        </is>
+      </c>
+      <c r="AB489" t="inlineStr">
+        <is>
+          <t>Auto-added from Globes scrape</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A3:AB3"/>
   <mergeCells count="4">

--- a/Lama_Israeli_Cyber_Deal_Database_v8.xlsx
+++ b/Lama_Israeli_Cyber_Deal_Database_v8.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB489"/>
+  <dimension ref="A1:AB490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -50074,6 +50074,108 @@
         </is>
       </c>
     </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Dream Security</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>dream.security</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>https://my.pitchbook.com/profile/510561-82/company/profile</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>AI-powered cyber defense — autonomous threat detection at national and enterprise scale</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>Tel Aviv</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>Security Operations</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>Shalev Hulio</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>8200</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>NSO Group (co-founder)</t>
+        </is>
+      </c>
+      <c r="O490" t="inlineStr">
+        <is>
+          <t>Government, critical infrastructure</t>
+        </is>
+      </c>
+      <c r="P490" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="Q490" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="R490" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U490" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="V490" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="W490" t="inlineStr">
+        <is>
+          <t>260.0</t>
+        </is>
+      </c>
+      <c r="AA490" t="inlineStr">
+        <is>
+          <t>https://en.globes.co.il/en/article-1001546297#utm_source=RSS</t>
+        </is>
+      </c>
+      <c r="AB490" t="inlineStr">
+        <is>
+          <t>Auto-added from Globes scrape</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A3:AB3"/>
   <mergeCells count="4">
